--- a/branches/migration/2026.0.3-template-v0.11.1/observations-summary.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/observations-summary.xlsx
@@ -464,7 +464,7 @@
     <t>MII PR Onkologie Prostata Gleason Grade Group</t>
   </si>
   <si>
-    <t>null#1812491000004107</t>
+    <t>null#1812491000004107, null#94734-1</t>
   </si>
   <si>
     <t>mii-pr-onko-prostate-gleason-score-gesamt</t>
@@ -473,7 +473,7 @@
     <t>MII PR Onkologie Prostata Gleason Score Gesamt</t>
   </si>
   <si>
-    <t>null#372278000</t>
+    <t>null#372278000, null#35266-6</t>
   </si>
   <si>
     <t>mii-pr-onko-residualstatus</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/observations-summary.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="205">
   <si>
     <t>Profile</t>
   </si>
@@ -594,6 +594,21 @@
   </si>
   <si>
     <t>null#21889-1, null#371479009</t>
+  </si>
+  <si>
+    <t>mii-pr-onko-tumormarker</t>
+  </si>
+  <si>
+    <t>MII PR Onkologie Tumormarker</t>
+  </si>
+  <si>
+    <t>LOINC#26436-6, Observation Category Codes#laboratory</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-tumormarker-loinc (extensible)</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, Rangeĵ, Ratioĵ</t>
   </si>
   <si>
     <t>mii-pr-onko-verlauf</t>
@@ -745,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3626,22 +3641,22 @@
         <v>195</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -3655,10 +3670,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>13</v>
@@ -3667,16 +3682,16 @@
         <v>13</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>18</v>
@@ -3693,7 +3708,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>13</v>
@@ -3702,7 +3717,7 @@
         <v>13</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>13</v>
@@ -3728,7 +3743,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>13</v>
@@ -3737,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>13</v>
@@ -3755,6 +3770,41 @@
         <v>13</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>13</v>
       </c>
     </row>
